--- a/Lab2/Таблица_60_тактов.xlsx
+++ b/Lab2/Таблица_60_тактов.xlsx
@@ -193,6 +193,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCC99FF"/>
       <color rgb="FFCE93D3"/>
       <color rgb="FF66CCFF"/>
       <color rgb="FFFFCCFF"/>
